--- a/file_classifier/category_map.xlsx
+++ b/file_classifier/category_map.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>계정과목</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+  <si>
+    <t>폴더명</t>
   </si>
   <si>
     <t>키워드</t>
@@ -31,18 +31,33 @@
     <t>재고자산</t>
   </si>
   <si>
+    <t>기타의유동자산</t>
+  </si>
+  <si>
     <t>유형자산</t>
   </si>
   <si>
     <t>매입채무</t>
   </si>
   <si>
+    <t>기타의유동부채</t>
+  </si>
+  <si>
     <t>차입금</t>
   </si>
   <si>
+    <t>퇴직급여충당부채</t>
+  </si>
+  <si>
     <t>매출</t>
   </si>
   <si>
+    <t>매출원가</t>
+  </si>
+  <si>
+    <t>판매비와관리비</t>
+  </si>
+  <si>
     <t>급여</t>
   </si>
   <si>
@@ -52,7 +67,16 @@
     <t>리스</t>
   </si>
   <si>
-    <t>잔액증명,통장,은행,cash,bank,잔고,예금</t>
+    <t>재무제표</t>
+  </si>
+  <si>
+    <t>별도보고서</t>
+  </si>
+  <si>
+    <t>연결보고서</t>
+  </si>
+  <si>
+    <t>잔액증명,통장,은행,cash,bank,잔고,예금, 이자수익</t>
   </si>
   <si>
     <t>채권,receivable,invoice,외상매출,AR</t>
@@ -61,25 +85,49 @@
     <t>재고,inventory,창고,실사,stock</t>
   </si>
   <si>
+    <t>미수금, 미수수익, 선급금, 선급부가세</t>
+  </si>
+  <si>
     <t>유형자산,설비,기계,건물,차량,취득,감가상각,PP&amp;E</t>
   </si>
   <si>
     <t>채무,payable,매입,AP,외상매입</t>
   </si>
   <si>
-    <t>차입,대출,loan,borrowing,금융기관</t>
+    <t>미지급금,선수금,미지급비용</t>
+  </si>
+  <si>
+    <t>차입,대출,loan,borrowing,금융기관, 이자비용</t>
+  </si>
+  <si>
+    <t>퇴직급여, 퇴충, 계리, 퇴직연금</t>
   </si>
   <si>
     <t>매출,revenue,sales,세금계산서,계산서</t>
   </si>
   <si>
+    <t>제조원가, 원가계산</t>
+  </si>
+  <si>
+    <t>복리후생비, 여비교통비, 수수료, 운반비</t>
+  </si>
+  <si>
     <t>급여,임금,salary,payroll,인건비,급료</t>
   </si>
   <si>
     <t>법인세,세금,tax,income tax,납부</t>
   </si>
   <si>
-    <t>리스,lease,임대,사용권,ROU</t>
+    <t>리스,lease,임대,사용권,ROU,사용권자산,리스자산</t>
+  </si>
+  <si>
+    <t>총계정원장, 재무상태표, 손익계산서, 현금흐름표</t>
+  </si>
+  <si>
+    <t>별도,별도정산서, 별도정산표, 별도dsd, 별도검토보고서, 별도감사보고서</t>
+  </si>
+  <si>
+    <t>연결,연결정산서, 연결정산표, 연결dsd, 연결검토보고서, 연결감사보고서</t>
   </si>
 </sst>
 </file>
@@ -437,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -453,7 +501,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -461,7 +509,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -469,7 +517,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -477,7 +525,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -485,7 +533,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -493,7 +541,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -501,7 +549,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -509,7 +557,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -517,7 +565,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -525,7 +573,71 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/file_classifier/category_map.xlsx
+++ b/file_classifier/category_map.xlsx
@@ -1,159 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
-  <si>
-    <t>폴더명</t>
-  </si>
-  <si>
-    <t>키워드</t>
-  </si>
-  <si>
-    <t>현금및현금성자산</t>
-  </si>
-  <si>
-    <t>매출채권</t>
-  </si>
-  <si>
-    <t>재고자산</t>
-  </si>
-  <si>
-    <t>기타의유동자산</t>
-  </si>
-  <si>
-    <t>유형자산</t>
-  </si>
-  <si>
-    <t>매입채무</t>
-  </si>
-  <si>
-    <t>기타의유동부채</t>
-  </si>
-  <si>
-    <t>차입금</t>
-  </si>
-  <si>
-    <t>퇴직급여충당부채</t>
-  </si>
-  <si>
-    <t>매출</t>
-  </si>
-  <si>
-    <t>매출원가</t>
-  </si>
-  <si>
-    <t>판매비와관리비</t>
-  </si>
-  <si>
-    <t>급여</t>
-  </si>
-  <si>
-    <t>법인세</t>
-  </si>
-  <si>
-    <t>리스</t>
-  </si>
-  <si>
-    <t>재무제표</t>
-  </si>
-  <si>
-    <t>별도보고서</t>
-  </si>
-  <si>
-    <t>연결보고서</t>
-  </si>
-  <si>
-    <t>잔액증명,통장,은행,cash,bank,잔고,예금, 이자수익</t>
-  </si>
-  <si>
-    <t>채권,receivable,invoice,외상매출,AR</t>
-  </si>
-  <si>
-    <t>재고,inventory,창고,실사,stock</t>
-  </si>
-  <si>
-    <t>미수금, 미수수익, 선급금, 선급부가세</t>
-  </si>
-  <si>
-    <t>유형자산,설비,기계,건물,차량,취득,감가상각,PP&amp;E</t>
-  </si>
-  <si>
-    <t>채무,payable,매입,AP,외상매입</t>
-  </si>
-  <si>
-    <t>미지급금,선수금,미지급비용</t>
-  </si>
-  <si>
-    <t>차입,대출,loan,borrowing,금융기관, 이자비용</t>
-  </si>
-  <si>
-    <t>퇴직급여, 퇴충, 계리, 퇴직연금</t>
-  </si>
-  <si>
-    <t>매출,revenue,sales,세금계산서,계산서</t>
-  </si>
-  <si>
-    <t>제조원가, 원가계산</t>
-  </si>
-  <si>
-    <t>복리후생비, 여비교통비, 수수료, 운반비</t>
-  </si>
-  <si>
-    <t>급여,임금,salary,payroll,인건비,급료</t>
-  </si>
-  <si>
-    <t>법인세,세금,tax,income tax,납부</t>
-  </si>
-  <si>
-    <t>리스,lease,임대,사용권,ROU,사용권자산,리스자산</t>
-  </si>
-  <si>
-    <t>총계정원장, 재무상태표, 손익계산서, 현금흐름표</t>
-  </si>
-  <si>
-    <t>별도,별도정산서, 별도정산표, 별도dsd, 별도검토보고서, 별도감사보고서</t>
-  </si>
-  <si>
-    <t>연결,연결정산서, 연결정산표, 연결dsd, 연결검토보고서, 연결감사보고서</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -187,16 +69,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -484,160 +433,252 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>폴더명</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>키워드</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>잔액증명,통장,은행,cash,bank,잔고,예금, 이자수익</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>매출채권</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>채권,receivable,invoice,외상매출,AR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>재고자산</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>재고,inventory,창고,실사,stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>기타의유동자산</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>미수금, 미수수익, 선급금, 선급부가세</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>유형자산,설비,기계,건물,차량,취득,감가상각,PP&amp;E</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>매입채무</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>채무,payable,매입,AP,외상매입</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>기타의유동부채</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>미지급금,선수금,미지급비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>차입금</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>차입,대출,loan,borrowing,금융기관, 이자비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>퇴직급여충당부채</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>퇴직급여, 퇴충, 계리, 퇴직연금</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>매출,revenue,sales,세금계산서,계산서</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>제조원가, 원가계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>판매비와관리비</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>복리후생비, 여비교통비, 수수료, 운반비</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>급여</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>급여,임금,salary,payroll,인건비,급료</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>법인세</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>법인세,세금,tax,income tax,납부</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>리스</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>리스,lease,임대,사용권,ROU,사용권자산,리스자산</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>재무제표</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>총계정원장, 재무상태표, 손익계산서, 현금흐름표</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>별도보고서</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>별도,별도정산서, 별도정산표, 별도dsd, 별도검토보고서, 별도감사보고서</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>연결보고서</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>연결,연결정산서, 연결정산표, 연결dsd, 연결검토보고서, 연결감사보고서</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>일반사항</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>조직도,법인등기,사업자등록,정관,법인인감,설립</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/file_classifier/category_map.xlsx
+++ b/file_classifier/category_map.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>매출,revenue,sales,세금계산서,계산서</t>
+          <t>매출,revenue,sales,세금계산서,계산서,부가세</t>
         </is>
       </c>
     </row>

--- a/file_classifier/category_map.xlsx
+++ b/file_classifier/category_map.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>조직도,법인등기,사업자등록,정관,법인인감,설립</t>
+          <t>조직도,법인등기,사업자등록,정관,법인인감,설립,주주</t>
         </is>
       </c>
     </row>

--- a/file_classifier/category_map.xlsx
+++ b/file_classifier/category_map.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>유형자산,설비,기계,건물,차량,취득,감가상각,PP&amp;E</t>
+          <t>유형자산,설비,기계,건물,차량,취득,감가상각,PP&amp;E,부동산</t>
         </is>
       </c>
     </row>

--- a/file_classifier/category_map.xlsx
+++ b/file_classifier/category_map.xlsx
@@ -636,12 +636,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>재무제표</t>
+          <t>재무제표 및 결산서</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>총계정원장, 재무상태표, 손익계산서, 현금흐름표</t>
+          <t>총계정원장, 재무상태표, 손익계산서, 현금흐름표,결산서,잔액명세서,재무제표</t>
         </is>
       </c>
     </row>

--- a/file_classifier/category_map.xlsx
+++ b/file_classifier/category_map.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>미수금, 미수수익, 선급금, 선급부가세</t>
+          <t>미수금, 미수수익, 선급금, 선급부가세,단기대여금</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>리스,lease,임대,사용권,ROU,사용권자산,리스자산</t>
+          <t>리스,lease,임대,사용권,ROU,사용권자산,리스자산,렌터카</t>
         </is>
       </c>
     </row>

--- a/file_classifier/category_map.xlsx
+++ b/file_classifier/category_map.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>차입,대출,loan,borrowing,금융기관, 이자비용</t>
+          <t>차입,대출,loan,borrowing,금융기관, 이자비용,전환사채</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>조직도,법인등기,사업자등록,정관,법인인감,설립,주주</t>
+          <t>조직도,법인등기,사업자등록,정관,법인인감,설립,주주,중소기업확인서</t>
         </is>
       </c>
     </row>
